--- a/xlsx/effect_program.xlsx
+++ b/xlsx/effect_program.xlsx
@@ -23,34 +23,34 @@
     <t xml:space="preserve">Augmenter l'âge légal de départ à la retraite, à 65 ans</t>
   </si>
   <si>
+    <t xml:space="preserve">Réduire l’aide au développement&lt;br&gt;pour les pays à bas revenus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maintenir les politiques climatiques du Green&lt;br&gt;Deal : prix carbone sur le pétrole et le gaz,&lt;br&gt;normes pour sortir des voitures thermiques</t>
   </si>
   <si>
-    <t xml:space="preserve">Réduire l’aide au développement&lt;br&gt;pour les pays à bas revenus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Régulariser les travailleurs&lt;br&gt;sans-papiers dans les métiers en tension</t>
   </si>
   <si>
     <t xml:space="preserve">Élire les députés à la proportionnelle</t>
   </si>
   <si>
+    <t xml:space="preserve">Restaurer l'âge légal de départ à la retraite à 62 ans</t>
+  </si>
+  <si>
     <t xml:space="preserve">Proposer à l'ONU une taxe internationale sur les&lt;br&gt;millionnaires, dont 30% financerait la santé et&lt;br&gt;l’éducation dans les pays à bas revenus</t>
   </si>
   <si>
-    <t xml:space="preserve">Restaurer l'âge légal de départ à la retraite à 62 ans</t>
-  </si>
-  <si>
     <t xml:space="preserve">Instaurer le Référendum d’Initiative Citoyenne (RIC) dès&lt;br&gt;qu'une proposition recueille 1 million de signatures</t>
   </si>
   <si>
+    <t xml:space="preserve">Restreindre l'accès aux aides sociales, à l'aide&lt;br&gt;médicale et aux logements sociaux pour les étrangers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Augmenter le SMIC de 10%, à 1600€ net par mois</t>
   </si>
   <si>
     <t xml:space="preserve">Pour les milliardaires, mettre fin à l'exonération&lt;br&gt;d'impôts sur l'héritage (pacte Dutreil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restreindre l'accès aux aides sociales, à l'aide&lt;br&gt;médicale et aux logements sociaux pour les étrangers</t>
   </si>
   <si>
     <t xml:space="preserve">Réduire le déficit public sous les 3% du PIB&lt;br&gt;et stabiliser l'endettement public d'ici 2032</t>
@@ -470,55 +470,55 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.183970945075845</v>
+        <v>0.174</v>
       </c>
       <c r="C2" t="n">
-        <v>0.319728553646545</v>
+        <v>0.306</v>
       </c>
       <c r="D2" t="n">
-        <v>0.127451454972758</v>
+        <v>0.103</v>
       </c>
       <c r="E2" t="n">
-        <v>0.105146302520496</v>
+        <v>0.123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.191801027214844</v>
+        <v>0.184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0392993406949469</v>
+        <v>0.043</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0907235052377827</v>
+        <v>0.124</v>
       </c>
       <c r="I2" t="n">
-        <v>0.124242455661579</v>
+        <v>0.089</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0447309531876728</v>
+        <v>0.046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0693016747620041</v>
+        <v>0.126</v>
       </c>
       <c r="L2" t="n">
-        <v>0.107806667965832</v>
+        <v>0.069</v>
       </c>
       <c r="M2" t="n">
-        <v>0.122560762634629</v>
+        <v>0.104</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0227613129472448</v>
+        <v>0.025</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0438039214847561</v>
+        <v>0.045</v>
       </c>
       <c r="P2" t="n">
-        <v>0.024807169002552</v>
+        <v>0.026</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0314527728470129</v>
+        <v>0.029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0293355748229399</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="3">
@@ -526,55 +526,55 @@
         <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>0.244113188485935</v>
+        <v>0.244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.214511550932113</v>
+        <v>0.217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.140795126809044</v>
+        <v>0.163</v>
       </c>
       <c r="E3" t="n">
-        <v>0.165423911032342</v>
+        <v>0.137</v>
       </c>
       <c r="F3" t="n">
-        <v>0.115782544474952</v>
+        <v>0.116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0690906181749522</v>
+        <v>0.067</v>
       </c>
       <c r="H3" t="n">
-        <v>0.10449346109557</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.118767280417583</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0822184200212059</v>
+        <v>0.081</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0929942516151783</v>
+        <v>0.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0789427484453612</v>
+        <v>0.095</v>
       </c>
       <c r="M3" t="n">
-        <v>0.114086532828265</v>
+        <v>0.078</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0363859031006696</v>
+        <v>0.035</v>
       </c>
       <c r="O3" t="n">
-        <v>0.049679282735332</v>
+        <v>0.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0318802139693673</v>
+        <v>0.036</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0349845822085608</v>
+        <v>0.035</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0383767833781493</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="4">
@@ -582,55 +582,55 @@
         <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>0.343713117252097</v>
+        <v>0.343</v>
       </c>
       <c r="C4" t="n">
-        <v>0.210358672926048</v>
+        <v>0.214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.36731781306532</v>
+        <v>0.362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.36249429278296</v>
+        <v>0.354</v>
       </c>
       <c r="F4" t="n">
-        <v>0.272417999772492</v>
+        <v>0.267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.414005162918468</v>
+        <v>0.405</v>
       </c>
       <c r="H4" t="n">
-        <v>0.269791545728294</v>
+        <v>0.218</v>
       </c>
       <c r="I4" t="n">
-        <v>0.214780156111426</v>
+        <v>0.267</v>
       </c>
       <c r="J4" t="n">
-        <v>0.314083661220044</v>
+        <v>0.309</v>
       </c>
       <c r="K4" t="n">
-        <v>0.260925566279108</v>
+        <v>0.188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.234663051065911</v>
+        <v>0.256</v>
       </c>
       <c r="M4" t="n">
-        <v>0.181633932670412</v>
+        <v>0.23</v>
       </c>
       <c r="N4" t="n">
-        <v>0.26384405369072</v>
+        <v>0.258</v>
       </c>
       <c r="O4" t="n">
-        <v>0.174368826244702</v>
+        <v>0.176</v>
       </c>
       <c r="P4" t="n">
-        <v>0.178047172626668</v>
+        <v>0.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.157843505218083</v>
+        <v>0.155</v>
       </c>
       <c r="R4" t="n">
-        <v>0.129182818686189</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="5">
@@ -638,55 +638,55 @@
         <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>0.156583572397827</v>
+        <v>0.167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.15426217568638</v>
+        <v>0.159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.254596891276564</v>
+        <v>0.225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.219074184418501</v>
+        <v>0.269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.30813867006523</v>
+        <v>0.316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.305098673313066</v>
+        <v>0.309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.299860906866146</v>
+        <v>0.284</v>
       </c>
       <c r="I5" t="n">
-        <v>0.291381812676209</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.322764801962549</v>
+        <v>0.326</v>
       </c>
       <c r="K5" t="n">
-        <v>0.321833705526337</v>
+        <v>0.242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.241905915911453</v>
+        <v>0.324</v>
       </c>
       <c r="M5" t="n">
-        <v>0.242782174600576</v>
+        <v>0.242</v>
       </c>
       <c r="N5" t="n">
-        <v>0.398850441472581</v>
+        <v>0.394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.217120169515719</v>
+        <v>0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>0.437767202324764</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.333708826591115</v>
+        <v>0.339</v>
       </c>
       <c r="R5" t="n">
-        <v>0.320747061153041</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="6">
@@ -694,55 +694,55 @@
         <v>22</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0716191767882959</v>
+        <v>0.072</v>
       </c>
       <c r="C6" t="n">
-        <v>0.101139046808914</v>
+        <v>0.104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.109838713876314</v>
+        <v>0.147</v>
       </c>
       <c r="E6" t="n">
-        <v>0.147861309245701</v>
+        <v>0.117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.111859758472483</v>
+        <v>0.117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.172506204898568</v>
+        <v>0.176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.235130581072208</v>
+        <v>0.249</v>
       </c>
       <c r="I6" t="n">
-        <v>0.250828295133204</v>
+        <v>0.244</v>
       </c>
       <c r="J6" t="n">
-        <v>0.236202163608528</v>
+        <v>0.238</v>
       </c>
       <c r="K6" t="n">
-        <v>0.254944801817373</v>
+        <v>0.324</v>
       </c>
       <c r="L6" t="n">
-        <v>0.336681616611443</v>
+        <v>0.256</v>
       </c>
       <c r="M6" t="n">
-        <v>0.338936597266117</v>
+        <v>0.346</v>
       </c>
       <c r="N6" t="n">
-        <v>0.278158288788785</v>
+        <v>0.288</v>
       </c>
       <c r="O6" t="n">
-        <v>0.515027800019491</v>
+        <v>0.515</v>
       </c>
       <c r="P6" t="n">
-        <v>0.327498242076648</v>
+        <v>0.333</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.442010313135228</v>
+        <v>0.442</v>
       </c>
       <c r="R6" t="n">
-        <v>0.482357761959681</v>
+        <v>0.485</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/effect_program.xlsx
+++ b/xlsx/effect_program.xlsx
@@ -23,34 +23,34 @@
     <t xml:space="preserve">Augmenter l'âge légal de départ à la retraite, à 65 ans</t>
   </si>
   <si>
+    <t xml:space="preserve">Maintenir les politiques climatiques du Green&lt;br&gt;Deal : prix carbone sur le pétrole et le gaz,&lt;br&gt;normes pour sortir des voitures thermiques</t>
+  </si>
+  <si>
     <t xml:space="preserve">Réduire l’aide au développement&lt;br&gt;pour les pays à bas revenus</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenir les politiques climatiques du Green&lt;br&gt;Deal : prix carbone sur le pétrole et le gaz,&lt;br&gt;normes pour sortir des voitures thermiques</t>
-  </si>
-  <si>
     <t xml:space="preserve">Régulariser les travailleurs&lt;br&gt;sans-papiers dans les métiers en tension</t>
   </si>
   <si>
     <t xml:space="preserve">Élire les députés à la proportionnelle</t>
   </si>
   <si>
+    <t xml:space="preserve">Proposer à l'ONU une taxe internationale sur les&lt;br&gt;millionnaires, dont 30% financerait la santé et&lt;br&gt;l’éducation dans les pays à bas revenus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restaurer l'âge légal de départ à la retraite à 62 ans</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposer à l'ONU une taxe internationale sur les&lt;br&gt;millionnaires, dont 30% financerait la santé et&lt;br&gt;l’éducation dans les pays à bas revenus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Instaurer le Référendum d’Initiative Citoyenne (RIC) dès&lt;br&gt;qu'une proposition recueille 1 million de signatures</t>
   </si>
   <si>
+    <t xml:space="preserve">Augmenter le SMIC de 10%, à 1600€ net par mois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour les milliardaires, mettre fin à l'exonération&lt;br&gt;d'impôts sur l'héritage (pacte Dutreil)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restreindre l'accès aux aides sociales, à l'aide&lt;br&gt;médicale et aux logements sociaux pour les étrangers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augmenter le SMIC de 10%, à 1600€ net par mois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour les milliardaires, mettre fin à l'exonération&lt;br&gt;d'impôts sur l'héritage (pacte Dutreil)</t>
   </si>
   <si>
     <t xml:space="preserve">Réduire le déficit public sous les 3% du PIB&lt;br&gt;et stabiliser l'endettement public d'ici 2032</t>
@@ -470,55 +470,55 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.174</v>
+        <v>0.183970945075845</v>
       </c>
       <c r="C2" t="n">
-        <v>0.306</v>
+        <v>0.319728553646545</v>
       </c>
       <c r="D2" t="n">
-        <v>0.103</v>
+        <v>0.127451454972758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.123</v>
+        <v>0.105146302520496</v>
       </c>
       <c r="F2" t="n">
-        <v>0.184</v>
+        <v>0.191801027214844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.043</v>
+        <v>0.0392993406949469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.124</v>
+        <v>0.0907235052377827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.089</v>
+        <v>0.124242455661579</v>
       </c>
       <c r="J2" t="n">
-        <v>0.046</v>
+        <v>0.0447309531876728</v>
       </c>
       <c r="K2" t="n">
-        <v>0.126</v>
+        <v>0.0693016747620041</v>
       </c>
       <c r="L2" t="n">
-        <v>0.069</v>
+        <v>0.107806667965832</v>
       </c>
       <c r="M2" t="n">
-        <v>0.104</v>
+        <v>0.122560762634629</v>
       </c>
       <c r="N2" t="n">
-        <v>0.025</v>
+        <v>0.0227613129472448</v>
       </c>
       <c r="O2" t="n">
-        <v>0.045</v>
+        <v>0.0438039214847561</v>
       </c>
       <c r="P2" t="n">
-        <v>0.026</v>
+        <v>0.024807169002552</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.029</v>
+        <v>0.0314527728470129</v>
       </c>
       <c r="R2" t="n">
-        <v>0.027</v>
+        <v>0.0293355748229399</v>
       </c>
     </row>
     <row r="3">
@@ -526,55 +526,55 @@
         <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>0.244</v>
+        <v>0.244113188485935</v>
       </c>
       <c r="C3" t="n">
-        <v>0.217</v>
+        <v>0.214511550932113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.163</v>
+        <v>0.140795126809044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.137</v>
+        <v>0.165423911032342</v>
       </c>
       <c r="F3" t="n">
-        <v>0.116</v>
+        <v>0.115782544474952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.067</v>
+        <v>0.0690906181749522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.10449346109557</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.118767280417583</v>
       </c>
       <c r="J3" t="n">
-        <v>0.081</v>
+        <v>0.0822184200212059</v>
       </c>
       <c r="K3" t="n">
-        <v>0.12</v>
+        <v>0.0929942516151783</v>
       </c>
       <c r="L3" t="n">
-        <v>0.095</v>
+        <v>0.0789427484453612</v>
       </c>
       <c r="M3" t="n">
-        <v>0.078</v>
+        <v>0.114086532828265</v>
       </c>
       <c r="N3" t="n">
-        <v>0.035</v>
+        <v>0.0363859031006696</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05</v>
+        <v>0.049679282735332</v>
       </c>
       <c r="P3" t="n">
-        <v>0.036</v>
+        <v>0.0318802139693673</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.035</v>
+        <v>0.0349845822085608</v>
       </c>
       <c r="R3" t="n">
-        <v>0.041</v>
+        <v>0.0383767833781493</v>
       </c>
     </row>
     <row r="4">
@@ -582,55 +582,55 @@
         <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>0.343</v>
+        <v>0.343713117252097</v>
       </c>
       <c r="C4" t="n">
-        <v>0.214</v>
+        <v>0.210358672926048</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362</v>
+        <v>0.36731781306532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.354</v>
+        <v>0.36249429278296</v>
       </c>
       <c r="F4" t="n">
-        <v>0.267</v>
+        <v>0.272417999772492</v>
       </c>
       <c r="G4" t="n">
-        <v>0.405</v>
+        <v>0.414005162918468</v>
       </c>
       <c r="H4" t="n">
-        <v>0.218</v>
+        <v>0.269791545728294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.267</v>
+        <v>0.214780156111426</v>
       </c>
       <c r="J4" t="n">
-        <v>0.309</v>
+        <v>0.314083661220044</v>
       </c>
       <c r="K4" t="n">
-        <v>0.188</v>
+        <v>0.260925566279108</v>
       </c>
       <c r="L4" t="n">
-        <v>0.256</v>
+        <v>0.234663051065911</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23</v>
+        <v>0.181633932670412</v>
       </c>
       <c r="N4" t="n">
-        <v>0.258</v>
+        <v>0.26384405369072</v>
       </c>
       <c r="O4" t="n">
-        <v>0.176</v>
+        <v>0.174368826244702</v>
       </c>
       <c r="P4" t="n">
-        <v>0.17</v>
+        <v>0.178047172626668</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.155</v>
+        <v>0.157843505218083</v>
       </c>
       <c r="R4" t="n">
-        <v>0.13</v>
+        <v>0.129182818686189</v>
       </c>
     </row>
     <row r="5">
@@ -638,55 +638,55 @@
         <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>0.167</v>
+        <v>0.156583572397827</v>
       </c>
       <c r="C5" t="n">
-        <v>0.159</v>
+        <v>0.15426217568638</v>
       </c>
       <c r="D5" t="n">
-        <v>0.225</v>
+        <v>0.254596891276564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.269</v>
+        <v>0.219074184418501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.316</v>
+        <v>0.30813867006523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.309</v>
+        <v>0.305098673313066</v>
       </c>
       <c r="H5" t="n">
-        <v>0.284</v>
+        <v>0.299860906866146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.291381812676209</v>
       </c>
       <c r="J5" t="n">
-        <v>0.326</v>
+        <v>0.322764801962549</v>
       </c>
       <c r="K5" t="n">
-        <v>0.242</v>
+        <v>0.321833705526337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.324</v>
+        <v>0.241905915911453</v>
       </c>
       <c r="M5" t="n">
-        <v>0.242</v>
+        <v>0.242782174600576</v>
       </c>
       <c r="N5" t="n">
-        <v>0.394</v>
+        <v>0.398850441472581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.214</v>
+        <v>0.217120169515719</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>0.437767202324764</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.339</v>
+        <v>0.333708826591115</v>
       </c>
       <c r="R5" t="n">
-        <v>0.317</v>
+        <v>0.320747061153041</v>
       </c>
     </row>
     <row r="6">
@@ -694,55 +694,55 @@
         <v>22</v>
       </c>
       <c r="B6" t="n">
-        <v>0.072</v>
+        <v>0.0716191767882959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.104</v>
+        <v>0.101139046808914</v>
       </c>
       <c r="D6" t="n">
-        <v>0.147</v>
+        <v>0.109838713876314</v>
       </c>
       <c r="E6" t="n">
-        <v>0.117</v>
+        <v>0.147861309245701</v>
       </c>
       <c r="F6" t="n">
-        <v>0.117</v>
+        <v>0.111859758472483</v>
       </c>
       <c r="G6" t="n">
-        <v>0.176</v>
+        <v>0.172506204898568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.249</v>
+        <v>0.235130581072208</v>
       </c>
       <c r="I6" t="n">
-        <v>0.244</v>
+        <v>0.250828295133204</v>
       </c>
       <c r="J6" t="n">
-        <v>0.238</v>
+        <v>0.236202163608528</v>
       </c>
       <c r="K6" t="n">
-        <v>0.324</v>
+        <v>0.254944801817373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.256</v>
+        <v>0.336681616611443</v>
       </c>
       <c r="M6" t="n">
-        <v>0.346</v>
+        <v>0.338936597266117</v>
       </c>
       <c r="N6" t="n">
-        <v>0.288</v>
+        <v>0.278158288788785</v>
       </c>
       <c r="O6" t="n">
-        <v>0.515</v>
+        <v>0.515027800019491</v>
       </c>
       <c r="P6" t="n">
-        <v>0.333</v>
+        <v>0.327498242076648</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.442</v>
+        <v>0.442010313135228</v>
       </c>
       <c r="R6" t="n">
-        <v>0.485</v>
+        <v>0.482357761959681</v>
       </c>
     </row>
   </sheetData>
